--- a/notebooks/01_first_analysis/table_5_3_group_averages.xlsx
+++ b/notebooks/01_first_analysis/table_5_3_group_averages.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,25 +424,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>BLEU GOLD</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>SARI</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>BERTScore F1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MeaningBERT</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>RoBERTa Sense</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
+        <is>
+          <t>Fernandez Huerta Index (Original)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Fernandez Huerta Index (Gold)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Fernandez Huerta Index (Adapted)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>Compliance (%)</t>
         </is>
@@ -455,19 +470,28 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="C2" t="n">
         <v>46.706</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.744</v>
-      </c>
       <c r="D2" t="n">
-        <v>87.428</v>
+        <v>0.748</v>
       </c>
       <c r="E2" t="n">
-        <v>0.99</v>
+        <v>89.152</v>
       </c>
       <c r="F2" t="n">
-        <v>94.167</v>
+        <v>74.96899999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>93.80800000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>99.003</v>
+      </c>
+      <c r="I2" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +501,28 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C3" t="n">
         <v>50.782</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.76</v>
-      </c>
       <c r="D3" t="n">
-        <v>85.178</v>
+        <v>0.773</v>
       </c>
       <c r="E3" t="n">
-        <v>0.985</v>
+        <v>88.31699999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>78.333</v>
+        <v>74.96899999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>93.80800000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>95.56</v>
+      </c>
+      <c r="I3" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +532,28 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="C4" t="n">
         <v>41.813</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.875</v>
-      </c>
       <c r="D4" t="n">
-        <v>93.14100000000001</v>
+        <v>0.73</v>
       </c>
       <c r="E4" t="n">
-        <v>0.978</v>
+        <v>88.76300000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>74.96899999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>93.80800000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>85.176</v>
+      </c>
+      <c r="I4" t="n">
+        <v>84.444</v>
       </c>
     </row>
   </sheetData>
